--- a/阵营/攻防监控防冲突.xlsx
+++ b/阵营/攻防监控防冲突.xlsx
@@ -4677,7 +4677,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4803,13 +4803,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5309,7 +5302,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5318,10 +5311,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5333,7 +5326,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5345,7 +5338,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5357,7 +5350,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5369,7 +5362,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5381,7 +5374,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5888,7 +5881,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="16" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786119176000,</v>
+        <v>nTimeStamp = 1790272308000,</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>11</v>

--- a/阵营/攻防监控防冲突.xlsx
+++ b/阵营/攻防监控防冲突.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1542">
   <si>
     <t>__meta = {</t>
   </si>
@@ -4650,6 +4650,9 @@
   </si>
   <si>
     <t>^【(.*)】据点大旗(.*)重置回初始位置！\n</t>
+  </si>
+  <si>
+    <t>防止冲突</t>
   </si>
   <si>
     <t>^恶人谷的【(.*)】帮会成功占领【(.*)】据点！(.*)</t>
@@ -4680,13 +4683,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5251,28 +5248,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5281,49 +5281,46 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5335,7 +5332,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5347,7 +5344,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5359,7 +5356,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5371,7 +5368,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5383,7 +5380,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5395,7 +5392,7 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5403,7 +5400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5412,13 +5409,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5451,19 +5448,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="22" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="22" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5472,7 +5469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5481,19 +5478,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="23" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="23" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5508,7 +5505,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -5897,7 +5894,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1792519201000,</v>
+        <v>nTimeStamp = 1792592795000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -16244,69 +16241,84 @@
       <c r="C3" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>1535</v>
+      </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",[20]={},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="C4" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="D4" s="1"/>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^恶人谷的【(.*)】帮会成功占领【(.*)】据点！(.*)",[20]={},},</v>
+        <v>{szContent="^恶人谷的【(.*)】帮会成功占领【(.*)】据点！(.*)",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="C5" s="1" t="s">
-        <v>1536</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>1537</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1535</v>
+      </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^浩气盟的【(.*)】帮会成功占领【(.*)】据点！(.*)",[20]={},},</v>
+        <v>{szContent="^浩气盟的【(.*)】帮会成功占领【(.*)】据点！(.*)",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="C6" s="1" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D6" s="1"/>
+        <v>1538</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1535</v>
+      </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^恶人谷位于(.*)的【(.*)据点】大旗被夺，10分钟后若未能夺回大旗，则会丢失此据点！\n",[20]={},},</v>
+        <v>{szContent="^恶人谷位于(.*)的【(.*)据点】大旗被夺，10分钟后若未能夺回大旗，则会丢失此据点！\n",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="C7" s="1" t="s">
-        <v>1538</v>
-      </c>
-      <c r="D7" s="1"/>
+        <v>1539</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1535</v>
+      </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^浩气盟位于(.*)的【(.*)据点】大旗被夺，10分钟后若未能夺回大旗，则会丢失此据点！\n",[20]={},},</v>
+        <v>{szContent="^浩气盟位于(.*)的【(.*)据点】大旗被夺，10分钟后若未能夺回大旗，则会丢失此据点！\n",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="C8" s="1" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>1540</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1535</v>
+      </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^江湖快报！(.*)据点粮仓被一群恶人谷人士洗劫，损失一半据点资金。\n",[20]={},},</v>
+        <v>{szContent="^江湖快报！(.*)据点粮仓被一群恶人谷人士洗劫，损失一半据点资金。\n",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="C9" s="1" t="s">
-        <v>1540</v>
+        <v>1541</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1535</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^江湖快报！(.*)据点粮仓被一群浩气盟人士洗劫，损失一半据点资金。\n",[20]={},},</v>
+        <v>{szContent="^江湖快报！(.*)据点粮仓被一群浩气盟人士洗劫，损失一半据点资金。\n",szNote="防止冲突",[20]={},},</v>
       </c>
     </row>
     <row r="10" spans="1:15">
